--- a/MI_scen2_calculations.xlsx
+++ b/MI_scen2_calculations.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7767ba86a98102bc/TEP4290/Project/TEP4290-project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="8_{3C4CCC96-B1F8-44E1-AC5F-D3EA57398C1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CF610745-CB01-4424-8319-6308A3D61B7B}"/>
+  <xr:revisionPtr revIDLastSave="66" documentId="8_{3C4CCC96-B1F8-44E1-AC5F-D3EA57398C1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7566C6C4-23CD-4A91-A568-95FE5AAB733F}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="14235" xr2:uid="{C721BC97-D025-1F49-9F9A-FF54A8AB1673}"/>
   </bookViews>
@@ -104,9 +104,6 @@
     <t>Ratio brick</t>
   </si>
   <si>
-    <t>Ratio rest</t>
-  </si>
-  <si>
     <t>Sum rest</t>
   </si>
   <si>
@@ -120,6 +117,9 @@
   </si>
   <si>
     <t>Ratio copper/rest</t>
+  </si>
+  <si>
+    <t>Ratio steel</t>
   </si>
 </sst>
 </file>
@@ -237,6 +237,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -616,19 +620,19 @@
         <v>18</v>
       </c>
       <c r="R1" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="S1" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="S1" s="5" t="s">
+      <c r="T1" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="T1" s="5" t="s">
+      <c r="U1" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="U1" s="5" t="s">
+      <c r="V1" s="5" t="s">
         <v>26</v>
-      </c>
-      <c r="V1" s="5" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.5">
@@ -1148,7 +1152,7 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A22" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="B22">
         <v>0.05</v>
